--- a/prix/motip-spray.xlsx
+++ b/prix/motip-spray.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7B1C28-04FA-46A3-98A2-EDA2B3D8EE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53A7717-E8C6-4801-A02C-39EE9423D186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -3575,7 +3575,7 @@
         <v>42</v>
       </c>
       <c r="F38" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -6795,7 +6795,7 @@
         <v>203</v>
       </c>
       <c r="F199" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -7050,7 +7050,7 @@
         <v>219</v>
       </c>
       <c r="F215" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
@@ -7080,7 +7080,7 @@
         <v>221</v>
       </c>
       <c r="F217" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -7110,7 +7110,7 @@
         <v>223</v>
       </c>
       <c r="F219" s="13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -7170,7 +7170,7 @@
         <v>227</v>
       </c>
       <c r="F223" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/motip-spray.xlsx
+++ b/prix/motip-spray.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53A7717-E8C6-4801-A02C-39EE9423D186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D302272A-284E-4E48-BE63-C7AF47E6543C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -2857,7 +2857,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2875,7 +2875,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="13">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3569,13 +3569,13 @@
         <v>569</v>
       </c>
       <c r="D38" s="14">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>42</v>
       </c>
       <c r="F38" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -3675,7 +3675,7 @@
         <v>47</v>
       </c>
       <c r="F43" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3755,7 +3755,7 @@
         <v>51</v>
       </c>
       <c r="F47" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3775,7 +3775,7 @@
         <v>52</v>
       </c>
       <c r="F48" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -3835,7 +3835,7 @@
         <v>55</v>
       </c>
       <c r="F51" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -4055,7 +4055,7 @@
         <v>66</v>
       </c>
       <c r="F62" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -4175,7 +4175,7 @@
         <v>72</v>
       </c>
       <c r="F68" s="13">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -5055,7 +5055,7 @@
         <v>116</v>
       </c>
       <c r="F112" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -5149,13 +5149,13 @@
         <v>721</v>
       </c>
       <c r="D117" s="14">
-        <v>10.47</v>
+        <v>13.75</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>121</v>
       </c>
       <c r="F117" s="13">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -5955,7 +5955,7 @@
         <v>161</v>
       </c>
       <c r="F157" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -6415,7 +6415,7 @@
         <v>184</v>
       </c>
       <c r="F180" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -6595,7 +6595,7 @@
         <v>193</v>
       </c>
       <c r="F189" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
@@ -6789,13 +6789,13 @@
         <v>656</v>
       </c>
       <c r="D199" s="14">
-        <v>17.5</v>
+        <v>18.670000000000002</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>203</v>
       </c>
       <c r="F199" s="13">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -6975,7 +6975,7 @@
         <v>214</v>
       </c>
       <c r="F210" s="13">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -7044,13 +7044,13 @@
         <v>499</v>
       </c>
       <c r="D215" s="14">
-        <v>12.780000000000001</v>
+        <v>13.620000000000001</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>219</v>
       </c>
       <c r="F215" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
@@ -7059,13 +7059,13 @@
         <v>500</v>
       </c>
       <c r="D216" s="14">
-        <v>11.34</v>
+        <v>12.09</v>
       </c>
       <c r="E216" s="9" t="s">
         <v>220</v>
       </c>
       <c r="F216" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -7080,7 +7080,7 @@
         <v>221</v>
       </c>
       <c r="F217" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -7104,13 +7104,13 @@
         <v>503</v>
       </c>
       <c r="D219" s="14">
-        <v>11.34</v>
+        <v>12.09</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>223</v>
       </c>
       <c r="F219" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -7164,13 +7164,13 @@
         <v>507</v>
       </c>
       <c r="D223" s="14">
-        <v>13.42</v>
+        <v>13.620000000000001</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>227</v>
       </c>
       <c r="F223" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -7209,13 +7209,13 @@
         <v>510</v>
       </c>
       <c r="D226" s="14">
-        <v>11.9</v>
+        <v>12.09</v>
       </c>
       <c r="E226" s="9" t="s">
         <v>230</v>
       </c>
       <c r="F226" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -7245,7 +7245,7 @@
         <v>232</v>
       </c>
       <c r="F228" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -8075,7 +8075,7 @@
         <v>286</v>
       </c>
       <c r="F282" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/motip-spray.xlsx
+++ b/prix/motip-spray.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D302272A-284E-4E48-BE63-C7AF47E6543C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79CFC80-D447-47BE-BFC2-E874BB024B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -2469,10 +2469,10 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2850,14 +2850,14 @@
       <c r="C2" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>8.57</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="13">
-        <v>4</v>
+      <c r="F2" s="14">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2868,13 +2868,13 @@
       <c r="C3" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>9.0500000000000007</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="14">
         <v>8</v>
       </c>
     </row>
@@ -2888,13 +2888,13 @@
       <c r="C4" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>9.66</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="14">
         <v>3</v>
       </c>
     </row>
@@ -2908,13 +2908,13 @@
       <c r="C5" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>9.99</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <v>3</v>
       </c>
     </row>
@@ -2928,13 +2928,13 @@
       <c r="C6" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>9.66</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <v>3</v>
       </c>
     </row>
@@ -2948,13 +2948,13 @@
       <c r="C7" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>9.66</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <v>2</v>
       </c>
     </row>
@@ -2968,13 +2968,13 @@
       <c r="C8" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>10</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>4</v>
       </c>
     </row>
@@ -2988,13 +2988,13 @@
       <c r="C9" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>9.99</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3008,13 +3008,13 @@
       <c r="C10" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>9.66</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <v>0</v>
       </c>
     </row>
@@ -3028,13 +3028,13 @@
       <c r="C11" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>9.66</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3048,13 +3048,13 @@
       <c r="C12" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>10.5</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3068,13 +3068,13 @@
       <c r="C13" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>9.66</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
       <c r="C14" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>10.5</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <v>6</v>
       </c>
     </row>
@@ -3108,13 +3108,13 @@
       <c r="C15" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>9.66</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3128,13 +3128,13 @@
       <c r="C16" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>10.5</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3148,13 +3148,13 @@
       <c r="C17" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>10</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3168,13 +3168,13 @@
       <c r="C18" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="13">
         <v>9.66</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3188,13 +3188,13 @@
       <c r="C19" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>9.99</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3208,13 +3208,13 @@
       <c r="C20" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>10</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>5</v>
       </c>
     </row>
@@ -3228,13 +3228,13 @@
       <c r="C21" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>9.99</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3248,13 +3248,13 @@
       <c r="C22" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>10</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3268,13 +3268,13 @@
       <c r="C23" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>9.66</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3288,13 +3288,13 @@
       <c r="C24" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="13">
         <v>9.66</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3308,13 +3308,13 @@
       <c r="C25" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>9.66</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3328,14 +3328,14 @@
       <c r="C26" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>9.99</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="13">
-        <v>3</v>
+      <c r="F26" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3348,13 +3348,13 @@
       <c r="C27" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <v>9.99</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="14">
         <v>14</v>
       </c>
     </row>
@@ -3368,14 +3368,14 @@
       <c r="C28" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="D28" s="14">
-        <v>9.66</v>
+      <c r="D28" s="13">
+        <v>10.5</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="13">
-        <v>3</v>
+      <c r="F28" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -3388,14 +3388,14 @@
       <c r="C29" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D29" s="14">
-        <v>9.66</v>
+      <c r="D29" s="13">
+        <v>10.5</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="13">
-        <v>6</v>
+      <c r="F29" s="14">
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3408,13 +3408,13 @@
       <c r="C30" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="13">
         <v>10</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <v>5</v>
       </c>
     </row>
@@ -3428,13 +3428,13 @@
       <c r="C31" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13">
         <v>10</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <v>0</v>
       </c>
     </row>
@@ -3448,13 +3448,13 @@
       <c r="C32" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="13">
         <v>10</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <v>6</v>
       </c>
     </row>
@@ -3468,14 +3468,14 @@
       <c r="C33" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="13">
         <v>9.99</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="13">
-        <v>8</v>
+      <c r="F33" s="14">
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3488,13 +3488,13 @@
       <c r="C34" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="13">
         <v>9.66</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="14">
         <v>0</v>
       </c>
     </row>
@@ -3508,13 +3508,13 @@
       <c r="C35" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="13">
         <v>10</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="14">
         <v>5</v>
       </c>
     </row>
@@ -3528,13 +3528,13 @@
       <c r="C36" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="13">
         <v>9.66</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="14">
         <v>0</v>
       </c>
     </row>
@@ -3548,14 +3548,14 @@
       <c r="C37" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="13">
         <v>9.66</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="13">
-        <v>7</v>
+      <c r="F37" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -3568,13 +3568,13 @@
       <c r="C38" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="13">
         <v>10.5</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3588,13 +3588,13 @@
       <c r="C39" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="13">
         <v>16.47</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3608,14 +3608,14 @@
       <c r="C40" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="13">
         <v>17.04</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="13">
-        <v>3</v>
+      <c r="F40" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -3628,13 +3628,13 @@
       <c r="C41" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="13">
         <v>16.47</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3648,13 +3648,13 @@
       <c r="C42" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="13">
         <v>17.04</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3668,14 +3668,14 @@
       <c r="C43" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="13">
         <v>17.88</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="13">
-        <v>5</v>
+      <c r="F43" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3688,13 +3688,13 @@
       <c r="C44" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="13">
         <v>17.04</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3708,13 +3708,13 @@
       <c r="C45" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="13">
         <v>17.04</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3728,13 +3728,13 @@
       <c r="C46" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="13">
         <v>17.04</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3748,13 +3748,13 @@
       <c r="C47" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="13">
         <v>16.47</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3768,13 +3768,13 @@
       <c r="C48" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="13">
         <v>17.04</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3788,13 +3788,13 @@
       <c r="C49" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="13">
         <v>17.04</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3808,13 +3808,13 @@
       <c r="C50" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="13">
         <v>17.04</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3828,14 +3828,14 @@
       <c r="C51" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="D51" s="14">
-        <v>16.47</v>
+      <c r="D51" s="13">
+        <v>17.88</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="13">
-        <v>1</v>
+      <c r="F51" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -3848,13 +3848,13 @@
       <c r="C52" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="13">
         <v>16.47</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3868,13 +3868,13 @@
       <c r="C53" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="13">
         <v>16.47</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3888,13 +3888,13 @@
       <c r="C54" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="13">
         <v>16.47</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="14">
         <v>0</v>
       </c>
     </row>
@@ -3908,14 +3908,14 @@
       <c r="C55" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="13">
         <v>17.04</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="13">
-        <v>1</v>
+      <c r="F55" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -3928,13 +3928,13 @@
       <c r="C56" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="D56" s="14">
+      <c r="D56" s="13">
         <v>16.47</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <v>5</v>
       </c>
     </row>
@@ -3948,13 +3948,13 @@
       <c r="C57" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="D57" s="14">
+      <c r="D57" s="13">
         <v>17.04</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3968,13 +3968,13 @@
       <c r="C58" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D58" s="13">
         <v>16.47</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3988,13 +3988,13 @@
       <c r="C59" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D59" s="13">
         <v>17.900000000000002</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4008,13 +4008,13 @@
       <c r="C60" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="D60" s="14">
+      <c r="D60" s="13">
         <v>17.88</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4028,13 +4028,13 @@
       <c r="C61" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="D61" s="14">
+      <c r="D61" s="13">
         <v>17.04</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4048,14 +4048,14 @@
       <c r="C62" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="D62" s="14">
-        <v>16.47</v>
+      <c r="D62" s="13">
+        <v>17.88</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F62" s="13">
-        <v>0</v>
+      <c r="F62" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -4068,13 +4068,13 @@
       <c r="C63" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="D63" s="14">
+      <c r="D63" s="13">
         <v>16.47</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4088,13 +4088,13 @@
       <c r="C64" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="D64" s="14">
+      <c r="D64" s="13">
         <v>17.04</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4108,13 +4108,13 @@
       <c r="C65" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D65" s="14">
+      <c r="D65" s="13">
         <v>16.47</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4128,14 +4128,14 @@
       <c r="C66" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="D66" s="14">
+      <c r="D66" s="13">
         <v>17</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="13">
-        <v>2</v>
+      <c r="F66" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -4148,13 +4148,13 @@
       <c r="C67" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="D67" s="14">
+      <c r="D67" s="13">
         <v>17.900000000000002</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="14">
         <v>4</v>
       </c>
     </row>
@@ -4168,13 +4168,13 @@
       <c r="C68" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D68" s="14">
+      <c r="D68" s="13">
         <v>17.900000000000002</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="14">
         <v>4</v>
       </c>
     </row>
@@ -4188,14 +4188,14 @@
       <c r="C69" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="D69" s="14">
+      <c r="D69" s="13">
         <v>17.04</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F69" s="13">
-        <v>4</v>
+      <c r="F69" s="14">
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -4208,13 +4208,13 @@
       <c r="C70" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D70" s="14">
+      <c r="D70" s="13">
         <v>16.47</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="14">
         <v>6</v>
       </c>
     </row>
@@ -4228,13 +4228,13 @@
       <c r="C71" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D71" s="14">
+      <c r="D71" s="13">
         <v>17.04</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4248,13 +4248,13 @@
       <c r="C72" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="D72" s="14">
+      <c r="D72" s="13">
         <v>10.5</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="14">
         <v>6</v>
       </c>
     </row>
@@ -4268,13 +4268,13 @@
       <c r="C73" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="D73" s="14">
+      <c r="D73" s="13">
         <v>9.66</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4288,13 +4288,13 @@
       <c r="C74" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D74" s="14">
+      <c r="D74" s="13">
         <v>10</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="14">
         <v>6</v>
       </c>
     </row>
@@ -4308,13 +4308,13 @@
       <c r="C75" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="D75" s="14">
+      <c r="D75" s="13">
         <v>10</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4328,13 +4328,13 @@
       <c r="C76" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="D76" s="14">
+      <c r="D76" s="13">
         <v>6.05</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="14">
         <v>0</v>
       </c>
     </row>
@@ -4348,13 +4348,13 @@
       <c r="C77" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D77" s="14">
+      <c r="D77" s="13">
         <v>12.64</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4368,13 +4368,13 @@
       <c r="C78" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D78" s="14">
+      <c r="D78" s="13">
         <v>13.75</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4388,13 +4388,13 @@
       <c r="C79" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="D79" s="14">
+      <c r="D79" s="13">
         <v>12.64</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="14">
         <v>5</v>
       </c>
     </row>
@@ -4408,13 +4408,13 @@
       <c r="C80" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D80" s="14">
+      <c r="D80" s="13">
         <v>12.64</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4428,13 +4428,13 @@
       <c r="C81" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="D81" s="14">
+      <c r="D81" s="13">
         <v>12.64</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F81" s="13">
+      <c r="F81" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4448,13 +4448,13 @@
       <c r="C82" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="D82" s="14">
+      <c r="D82" s="13">
         <v>12.64</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4468,13 +4468,13 @@
       <c r="C83" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="D83" s="14">
+      <c r="D83" s="13">
         <v>12.64</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F83" s="13">
+      <c r="F83" s="14">
         <v>4</v>
       </c>
     </row>
@@ -4488,13 +4488,13 @@
       <c r="C84" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="D84" s="14">
+      <c r="D84" s="13">
         <v>12.64</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4508,13 +4508,13 @@
       <c r="C85" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="D85" s="14">
+      <c r="D85" s="13">
         <v>10.5</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4528,13 +4528,13 @@
       <c r="C86" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="D86" s="14">
+      <c r="D86" s="13">
         <v>10.5</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4548,13 +4548,13 @@
       <c r="C87" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="D87" s="14">
+      <c r="D87" s="13">
         <v>12.64</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F87" s="13">
+      <c r="F87" s="14">
         <v>6</v>
       </c>
     </row>
@@ -4568,13 +4568,13 @@
       <c r="C88" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D88" s="14">
+      <c r="D88" s="13">
         <v>12.64</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4588,13 +4588,13 @@
       <c r="C89" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="D89" s="14">
+      <c r="D89" s="13">
         <v>10.5</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F89" s="13">
+      <c r="F89" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4608,13 +4608,13 @@
       <c r="C90" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="D90" s="14">
+      <c r="D90" s="13">
         <v>12.64</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="14">
         <v>4</v>
       </c>
     </row>
@@ -4628,13 +4628,13 @@
       <c r="C91" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="D91" s="14">
+      <c r="D91" s="13">
         <v>12.64</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F91" s="13">
+      <c r="F91" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4648,13 +4648,13 @@
       <c r="C92" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="D92" s="14">
+      <c r="D92" s="13">
         <v>12.64</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F92" s="13">
+      <c r="F92" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4668,13 +4668,13 @@
       <c r="C93" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="D93" s="14">
+      <c r="D93" s="13">
         <v>12.64</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F93" s="13">
+      <c r="F93" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4688,13 +4688,13 @@
       <c r="C94" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="D94" s="14">
+      <c r="D94" s="13">
         <v>12.64</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F94" s="13">
+      <c r="F94" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4708,13 +4708,13 @@
       <c r="C95" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="D95" s="14">
+      <c r="D95" s="13">
         <v>12.64</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F95" s="13">
+      <c r="F95" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4728,13 +4728,13 @@
       <c r="C96" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D96" s="14">
+      <c r="D96" s="13">
         <v>12.64</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F96" s="13">
+      <c r="F96" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4748,13 +4748,13 @@
       <c r="C97" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="D97" s="14">
+      <c r="D97" s="13">
         <v>12.64</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F97" s="13">
+      <c r="F97" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
       <c r="C98" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="D98" s="14">
+      <c r="D98" s="13">
         <v>12.64</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4788,13 +4788,13 @@
       <c r="C99" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="D99" s="14">
+      <c r="D99" s="13">
         <v>12.64</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F99" s="13">
+      <c r="F99" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4808,13 +4808,13 @@
       <c r="C100" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="D100" s="14">
+      <c r="D100" s="13">
         <v>12.64</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F100" s="13">
+      <c r="F100" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4828,13 +4828,13 @@
       <c r="C101" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D101" s="14">
+      <c r="D101" s="13">
         <v>12.64</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F101" s="13">
+      <c r="F101" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4848,13 +4848,13 @@
       <c r="C102" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D102" s="14">
+      <c r="D102" s="13">
         <v>10.4</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F102" s="13">
+      <c r="F102" s="14">
         <v>0</v>
       </c>
     </row>
@@ -4868,13 +4868,13 @@
       <c r="C103" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="D103" s="14">
+      <c r="D103" s="13">
         <v>12.64</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F103" s="13">
+      <c r="F103" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4888,13 +4888,13 @@
       <c r="C104" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="D104" s="14">
+      <c r="D104" s="13">
         <v>12.64</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4908,13 +4908,13 @@
       <c r="C105" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="D105" s="14">
+      <c r="D105" s="13">
         <v>10.47</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F105" s="13">
+      <c r="F105" s="14">
         <v>6</v>
       </c>
     </row>
@@ -4928,13 +4928,13 @@
       <c r="C106" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="D106" s="14">
+      <c r="D106" s="13">
         <v>12.64</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="F106" s="13">
+      <c r="F106" s="14">
         <v>1</v>
       </c>
     </row>
@@ -4948,13 +4948,13 @@
       <c r="C107" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="D107" s="14">
+      <c r="D107" s="13">
         <v>12.64</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F107" s="13">
+      <c r="F107" s="14">
         <v>2</v>
       </c>
     </row>
@@ -4968,13 +4968,13 @@
       <c r="C108" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="D108" s="14">
+      <c r="D108" s="13">
         <v>12.64</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F108" s="13">
+      <c r="F108" s="14">
         <v>3</v>
       </c>
     </row>
@@ -4988,13 +4988,13 @@
       <c r="C109" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="D109" s="14">
+      <c r="D109" s="13">
         <v>12.64</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F109" s="13">
+      <c r="F109" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5008,13 +5008,13 @@
       <c r="C110" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="D110" s="14">
+      <c r="D110" s="13">
         <v>12.64</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F110" s="13">
+      <c r="F110" s="14">
         <v>5</v>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
       <c r="C111" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="D111" s="14">
+      <c r="D111" s="13">
         <v>12.64</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F111" s="13">
+      <c r="F111" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5048,14 +5048,14 @@
       <c r="C112" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="D112" s="14">
+      <c r="D112" s="13">
         <v>13.75</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F112" s="13">
-        <v>1</v>
+      <c r="F112" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -5068,13 +5068,13 @@
       <c r="C113" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="D113" s="14">
+      <c r="D113" s="13">
         <v>12.64</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F113" s="13">
+      <c r="F113" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5088,13 +5088,13 @@
       <c r="C114" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="D114" s="14">
+      <c r="D114" s="13">
         <v>13.08</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="F114" s="13">
+      <c r="F114" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5108,14 +5108,14 @@
       <c r="C115" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="D115" s="14">
+      <c r="D115" s="13">
         <v>13.08</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F115" s="13">
-        <v>3</v>
+      <c r="F115" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -5128,13 +5128,13 @@
       <c r="C116" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="D116" s="14">
+      <c r="D116" s="13">
         <v>13.75</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F116" s="13">
+      <c r="F116" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5148,13 +5148,13 @@
       <c r="C117" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="D117" s="14">
+      <c r="D117" s="13">
         <v>13.75</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F117" s="13">
+      <c r="F117" s="14">
         <v>6</v>
       </c>
     </row>
@@ -5168,13 +5168,13 @@
       <c r="C118" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D118" s="14">
+      <c r="D118" s="13">
         <v>12.64</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F118" s="13">
+      <c r="F118" s="14">
         <v>4</v>
       </c>
     </row>
@@ -5188,13 +5188,13 @@
       <c r="C119" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D119" s="14">
+      <c r="D119" s="13">
         <v>12.64</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F119" s="13">
+      <c r="F119" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5208,13 +5208,13 @@
       <c r="C120" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D120" s="14">
+      <c r="D120" s="13">
         <v>13.1</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F120" s="13">
+      <c r="F120" s="14">
         <v>4</v>
       </c>
     </row>
@@ -5228,13 +5228,13 @@
       <c r="C121" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D121" s="14">
+      <c r="D121" s="13">
         <v>12.64</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F121" s="13">
+      <c r="F121" s="14">
         <v>5</v>
       </c>
     </row>
@@ -5248,13 +5248,13 @@
       <c r="C122" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D122" s="14">
+      <c r="D122" s="13">
         <v>12.64</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F122" s="13">
+      <c r="F122" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5268,13 +5268,13 @@
       <c r="C123" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D123" s="14">
+      <c r="D123" s="13">
         <v>12.64</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F123" s="13">
+      <c r="F123" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5288,13 +5288,13 @@
       <c r="C124" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D124" s="14">
+      <c r="D124" s="13">
         <v>12.64</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F124" s="13">
+      <c r="F124" s="14">
         <v>1</v>
       </c>
     </row>
@@ -5308,13 +5308,13 @@
       <c r="C125" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D125" s="14">
+      <c r="D125" s="13">
         <v>13.75</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F125" s="13">
+      <c r="F125" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5328,13 +5328,13 @@
       <c r="C126" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D126" s="14">
+      <c r="D126" s="13">
         <v>12.64</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F126" s="13">
+      <c r="F126" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5348,13 +5348,13 @@
       <c r="C127" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D127" s="14">
+      <c r="D127" s="13">
         <v>13.75</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F127" s="13">
+      <c r="F127" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5368,13 +5368,13 @@
       <c r="C128" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D128" s="14">
+      <c r="D128" s="13">
         <v>12.64</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F128" s="13">
+      <c r="F128" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5388,13 +5388,13 @@
       <c r="C129" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="D129" s="14">
+      <c r="D129" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F129" s="13">
+      <c r="F129" s="14">
         <v>1</v>
       </c>
     </row>
@@ -5408,13 +5408,13 @@
       <c r="C130" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="D130" s="14">
+      <c r="D130" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F130" s="13">
+      <c r="F130" s="14">
         <v>1</v>
       </c>
     </row>
@@ -5428,13 +5428,13 @@
       <c r="C131" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D131" s="14">
+      <c r="D131" s="13">
         <v>18.350000000000001</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F131" s="13">
+      <c r="F131" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5448,13 +5448,13 @@
       <c r="C132" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="D132" s="14">
+      <c r="D132" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F132" s="13">
+      <c r="F132" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5468,13 +5468,13 @@
       <c r="C133" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="D133" s="14">
+      <c r="D133" s="13">
         <v>18.350000000000001</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F133" s="13">
+      <c r="F133" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5488,13 +5488,13 @@
       <c r="C134" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D134" s="14">
+      <c r="D134" s="13">
         <v>13.9</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F134" s="13">
+      <c r="F134" s="14">
         <v>5</v>
       </c>
     </row>
@@ -5508,13 +5508,13 @@
       <c r="C135" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="D135" s="14">
+      <c r="D135" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F135" s="13">
+      <c r="F135" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5528,13 +5528,13 @@
       <c r="C136" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="D136" s="14">
+      <c r="D136" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F136" s="13">
+      <c r="F136" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5548,13 +5548,13 @@
       <c r="C137" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="D137" s="14">
+      <c r="D137" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F137" s="13">
+      <c r="F137" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5568,13 +5568,13 @@
       <c r="C138" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="D138" s="14">
+      <c r="D138" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F138" s="13">
+      <c r="F138" s="14">
         <v>1</v>
       </c>
     </row>
@@ -5588,13 +5588,13 @@
       <c r="C139" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="D139" s="14">
+      <c r="D139" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F139" s="13">
+      <c r="F139" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5608,13 +5608,13 @@
       <c r="C140" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="D140" s="14">
+      <c r="D140" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F140" s="13">
+      <c r="F140" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5628,13 +5628,13 @@
       <c r="C141" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="D141" s="14">
+      <c r="D141" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F141" s="13">
+      <c r="F141" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5648,13 +5648,13 @@
       <c r="C142" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="D142" s="14">
+      <c r="D142" s="13">
         <v>18.37</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F142" s="13">
+      <c r="F142" s="14">
         <v>4</v>
       </c>
     </row>
@@ -5668,13 +5668,13 @@
       <c r="C143" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="D143" s="14">
+      <c r="D143" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F143" s="13">
+      <c r="F143" s="14">
         <v>4</v>
       </c>
     </row>
@@ -5688,13 +5688,13 @@
       <c r="C144" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D144" s="14">
+      <c r="D144" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F144" s="13">
+      <c r="F144" s="14">
         <v>1</v>
       </c>
     </row>
@@ -5708,13 +5708,13 @@
       <c r="C145" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="D145" s="14">
+      <c r="D145" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F145" s="13">
+      <c r="F145" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5728,13 +5728,13 @@
       <c r="C146" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D146" s="14">
+      <c r="D146" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E146" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F146" s="13">
+      <c r="F146" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5748,13 +5748,13 @@
       <c r="C147" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="D147" s="14">
+      <c r="D147" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F147" s="13">
+      <c r="F147" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5768,13 +5768,13 @@
       <c r="C148" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="D148" s="14">
+      <c r="D148" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E148" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F148" s="13">
+      <c r="F148" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5788,13 +5788,13 @@
       <c r="C149" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="D149" s="14">
+      <c r="D149" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F149" s="13">
+      <c r="F149" s="14">
         <v>4</v>
       </c>
     </row>
@@ -5808,13 +5808,13 @@
       <c r="C150" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="D150" s="14">
+      <c r="D150" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E150" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F150" s="13">
+      <c r="F150" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5828,13 +5828,13 @@
       <c r="C151" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="D151" s="14">
+      <c r="D151" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F151" s="13">
+      <c r="F151" s="14">
         <v>7</v>
       </c>
     </row>
@@ -5848,13 +5848,13 @@
       <c r="C152" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="D152" s="14">
+      <c r="D152" s="13">
         <v>17.5</v>
       </c>
       <c r="E152" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F152" s="13">
+      <c r="F152" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5868,13 +5868,13 @@
       <c r="C153" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="D153" s="14">
+      <c r="D153" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F153" s="13">
+      <c r="F153" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5888,13 +5888,13 @@
       <c r="C154" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="D154" s="14">
+      <c r="D154" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E154" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F154" s="13">
+      <c r="F154" s="14">
         <v>3</v>
       </c>
     </row>
@@ -5908,13 +5908,13 @@
       <c r="C155" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="D155" s="14">
+      <c r="D155" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F155" s="13">
+      <c r="F155" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5928,13 +5928,13 @@
       <c r="C156" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="D156" s="14">
+      <c r="D156" s="13">
         <v>18.37</v>
       </c>
       <c r="E156" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F156" s="13">
+      <c r="F156" s="14">
         <v>4</v>
       </c>
     </row>
@@ -5948,14 +5948,14 @@
       <c r="C157" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="D157" s="14">
-        <v>18.37</v>
+      <c r="D157" s="13">
+        <v>18.66</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F157" s="13">
-        <v>0</v>
+      <c r="F157" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -5968,13 +5968,13 @@
       <c r="C158" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="D158" s="14">
+      <c r="D158" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E158" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F158" s="13">
+      <c r="F158" s="14">
         <v>2</v>
       </c>
     </row>
@@ -5988,13 +5988,13 @@
       <c r="C159" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="D159" s="14">
+      <c r="D159" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F159" s="13">
+      <c r="F159" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6008,13 +6008,13 @@
       <c r="C160" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="D160" s="14">
+      <c r="D160" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E160" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F160" s="13">
+      <c r="F160" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6028,13 +6028,13 @@
       <c r="C161" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="D161" s="14">
+      <c r="D161" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F161" s="13">
+      <c r="F161" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6048,13 +6048,13 @@
       <c r="C162" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="D162" s="14">
+      <c r="D162" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E162" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F162" s="13">
+      <c r="F162" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6068,13 +6068,13 @@
       <c r="C163" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="D163" s="14">
+      <c r="D163" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F163" s="13">
+      <c r="F163" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6088,13 +6088,13 @@
       <c r="C164" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="D164" s="14">
+      <c r="D164" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F164" s="13">
+      <c r="F164" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6108,13 +6108,13 @@
       <c r="C165" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="D165" s="14">
+      <c r="D165" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F165" s="13">
+      <c r="F165" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6128,13 +6128,13 @@
       <c r="C166" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="D166" s="14">
+      <c r="D166" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E166" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F166" s="13">
+      <c r="F166" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6148,13 +6148,13 @@
       <c r="C167" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="D167" s="14">
+      <c r="D167" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F167" s="13">
+      <c r="F167" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6168,13 +6168,13 @@
       <c r="C168" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="D168" s="14">
+      <c r="D168" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E168" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F168" s="13">
+      <c r="F168" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6188,13 +6188,13 @@
       <c r="C169" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="D169" s="14">
+      <c r="D169" s="13">
         <v>18.37</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F169" s="13">
+      <c r="F169" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6208,13 +6208,13 @@
       <c r="C170" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="D170" s="14">
+      <c r="D170" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E170" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F170" s="13">
+      <c r="F170" s="14">
         <v>6</v>
       </c>
     </row>
@@ -6228,13 +6228,13 @@
       <c r="C171" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D171" s="14">
+      <c r="D171" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F171" s="13">
+      <c r="F171" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6248,13 +6248,13 @@
       <c r="C172" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="D172" s="14">
+      <c r="D172" s="13">
         <v>17.5</v>
       </c>
       <c r="E172" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F172" s="13">
+      <c r="F172" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6268,13 +6268,13 @@
       <c r="C173" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="D173" s="14">
+      <c r="D173" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F173" s="13">
+      <c r="F173" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6288,13 +6288,13 @@
       <c r="C174" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="D174" s="14">
+      <c r="D174" s="13">
         <v>17.48</v>
       </c>
       <c r="E174" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F174" s="13">
+      <c r="F174" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6308,13 +6308,13 @@
       <c r="C175" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="D175" s="14">
+      <c r="D175" s="13">
         <v>17.5</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F175" s="13">
+      <c r="F175" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6328,13 +6328,13 @@
       <c r="C176" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="D176" s="14">
+      <c r="D176" s="13">
         <v>17.5</v>
       </c>
       <c r="E176" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F176" s="13">
+      <c r="F176" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6348,13 +6348,13 @@
       <c r="C177" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="D177" s="14">
+      <c r="D177" s="13">
         <v>18.38</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F177" s="13">
+      <c r="F177" s="14">
         <v>6</v>
       </c>
     </row>
@@ -6368,13 +6368,13 @@
       <c r="C178" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="D178" s="14">
+      <c r="D178" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E178" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F178" s="13">
+      <c r="F178" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6388,13 +6388,13 @@
       <c r="C179" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="D179" s="14">
+      <c r="D179" s="13">
         <v>17.5</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="F179" s="13">
+      <c r="F179" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6408,14 +6408,14 @@
       <c r="C180" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="D180" s="14">
+      <c r="D180" s="13">
         <v>18.38</v>
       </c>
       <c r="E180" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F180" s="13">
-        <v>5</v>
+      <c r="F180" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -6428,13 +6428,13 @@
       <c r="C181" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="D181" s="14">
+      <c r="D181" s="13">
         <v>17.5</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F181" s="13">
+      <c r="F181" s="14">
         <v>6</v>
       </c>
     </row>
@@ -6448,13 +6448,13 @@
       <c r="C182" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="D182" s="14">
+      <c r="D182" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E182" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F182" s="13">
+      <c r="F182" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6468,13 +6468,13 @@
       <c r="C183" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="D183" s="14">
+      <c r="D183" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F183" s="13">
+      <c r="F183" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6488,13 +6488,13 @@
       <c r="C184" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D184" s="14">
+      <c r="D184" s="13">
         <v>17.5</v>
       </c>
       <c r="E184" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F184" s="13">
+      <c r="F184" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6508,13 +6508,13 @@
       <c r="C185" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="D185" s="14">
+      <c r="D185" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F185" s="13">
+      <c r="F185" s="14">
         <v>5</v>
       </c>
     </row>
@@ -6528,13 +6528,13 @@
       <c r="C186" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="D186" s="14">
+      <c r="D186" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E186" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="F186" s="13">
+      <c r="F186" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6548,13 +6548,13 @@
       <c r="C187" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="D187" s="14">
+      <c r="D187" s="13">
         <v>17.5</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="F187" s="13">
+      <c r="F187" s="14">
         <v>4</v>
       </c>
     </row>
@@ -6568,13 +6568,13 @@
       <c r="C188" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="D188" s="14">
+      <c r="D188" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E188" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F188" s="13">
+      <c r="F188" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6588,13 +6588,13 @@
       <c r="C189" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="D189" s="14">
+      <c r="D189" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F189" s="13">
+      <c r="F189" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6608,13 +6608,13 @@
       <c r="C190" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="D190" s="14">
+      <c r="D190" s="13">
         <v>17.5</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="F190" s="13">
+      <c r="F190" s="14">
         <v>6</v>
       </c>
     </row>
@@ -6628,13 +6628,13 @@
       <c r="C191" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="D191" s="14">
+      <c r="D191" s="13">
         <v>17.48</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F191" s="13">
+      <c r="F191" s="14">
         <v>5</v>
       </c>
     </row>
@@ -6648,13 +6648,13 @@
       <c r="C192" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="D192" s="14">
+      <c r="D192" s="13">
         <v>18.38</v>
       </c>
       <c r="E192" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="F192" s="13">
+      <c r="F192" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6668,13 +6668,13 @@
       <c r="C193" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D193" s="14">
+      <c r="D193" s="13">
         <v>17.5</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="F193" s="13">
+      <c r="F193" s="14">
         <v>4</v>
       </c>
     </row>
@@ -6688,13 +6688,13 @@
       <c r="C194" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="D194" s="14">
+      <c r="D194" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E194" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F194" s="13">
+      <c r="F194" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6708,13 +6708,13 @@
       <c r="C195" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="D195" s="14">
+      <c r="D195" s="13">
         <v>17.48</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="F195" s="13">
+      <c r="F195" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6728,13 +6728,13 @@
       <c r="C196" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="D196" s="14">
+      <c r="D196" s="13">
         <v>17.48</v>
       </c>
       <c r="E196" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="F196" s="13">
+      <c r="F196" s="14">
         <v>2</v>
       </c>
     </row>
@@ -6748,14 +6748,14 @@
       <c r="C197" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="D197" s="14">
+      <c r="D197" s="13">
         <v>18.38</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F197" s="13">
-        <v>6</v>
+      <c r="F197" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -6768,14 +6768,14 @@
       <c r="C198" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="D198" s="14">
-        <v>18.38</v>
+      <c r="D198" s="13">
+        <v>18.670000000000002</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F198" s="13">
-        <v>4</v>
+      <c r="F198" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -6788,13 +6788,13 @@
       <c r="C199" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="D199" s="14">
+      <c r="D199" s="13">
         <v>18.670000000000002</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F199" s="13">
+      <c r="F199" s="14">
         <v>5</v>
       </c>
     </row>
@@ -6808,13 +6808,13 @@
       <c r="C200" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="D200" s="14">
+      <c r="D200" s="13">
         <v>18.37</v>
       </c>
       <c r="E200" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F200" s="13">
+      <c r="F200" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6828,13 +6828,13 @@
       <c r="C201" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="D201" s="14">
+      <c r="D201" s="13">
         <v>18.37</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F201" s="13">
+      <c r="F201" s="14">
         <v>6</v>
       </c>
     </row>
@@ -6843,13 +6843,13 @@
       <c r="B202" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="D202" s="14">
+      <c r="D202" s="13">
         <v>7.95</v>
       </c>
       <c r="E202" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F202" s="13">
+      <c r="F202" s="14">
         <v>1</v>
       </c>
     </row>
@@ -6863,13 +6863,13 @@
       <c r="C203" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="D203" s="14">
+      <c r="D203" s="13">
         <v>7.95</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F203" s="13">
+      <c r="F203" s="14">
         <v>3</v>
       </c>
     </row>
@@ -6878,13 +6878,13 @@
       <c r="B204" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="D204" s="14">
+      <c r="D204" s="13">
         <v>2.7</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="F204" s="13">
+      <c r="F204" s="14">
         <v>0</v>
       </c>
     </row>
@@ -6893,13 +6893,13 @@
       <c r="B205" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="D205" s="14">
+      <c r="D205" s="13">
         <v>9.2000000000000011</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="F205" s="13">
+      <c r="F205" s="14">
         <v>0</v>
       </c>
     </row>
@@ -6908,13 +6908,13 @@
       <c r="B206" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="D206" s="14">
+      <c r="D206" s="13">
         <v>1.2</v>
       </c>
       <c r="E206" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="F206" s="13">
+      <c r="F206" s="14">
         <v>41</v>
       </c>
     </row>
@@ -6923,13 +6923,13 @@
       <c r="B207" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="D207" s="14">
+      <c r="D207" s="13">
         <v>4.8</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F207" s="13">
+      <c r="F207" s="14">
         <v>41</v>
       </c>
     </row>
@@ -6938,13 +6938,13 @@
       <c r="B208" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="D208" s="14">
+      <c r="D208" s="13">
         <v>1.9000000000000001</v>
       </c>
       <c r="E208" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F208" s="13">
+      <c r="F208" s="14">
         <v>12</v>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
       <c r="B209" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="D209" s="14">
+      <c r="D209" s="13">
         <v>4.5</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F209" s="13">
+      <c r="F209" s="14">
         <v>10</v>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
       <c r="B210" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="D210" s="14">
+      <c r="D210" s="13">
         <v>19.600000000000001</v>
       </c>
       <c r="E210" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="F210" s="13">
+      <c r="F210" s="14">
         <v>6</v>
       </c>
     </row>
@@ -6983,13 +6983,13 @@
       <c r="B211" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="D211" s="14">
+      <c r="D211" s="13">
         <v>3.9</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="F211" s="13">
+      <c r="F211" s="14">
         <v>0</v>
       </c>
     </row>
@@ -6998,13 +6998,13 @@
       <c r="B212" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="D212" s="14">
+      <c r="D212" s="13">
         <v>7.2</v>
       </c>
       <c r="E212" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="F212" s="13">
+      <c r="F212" s="14">
         <v>1</v>
       </c>
     </row>
@@ -7013,13 +7013,13 @@
       <c r="B213" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="D213" s="14">
+      <c r="D213" s="13">
         <v>1.69</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="F213" s="13">
+      <c r="F213" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7028,13 +7028,13 @@
       <c r="B214" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="D214" s="14">
+      <c r="D214" s="13">
         <v>5.4</v>
       </c>
       <c r="E214" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F214" s="13">
+      <c r="F214" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7043,13 +7043,13 @@
       <c r="B215" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="D215" s="14">
+      <c r="D215" s="13">
         <v>13.620000000000001</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F215" s="13">
+      <c r="F215" s="14">
         <v>5</v>
       </c>
     </row>
@@ -7058,13 +7058,13 @@
       <c r="B216" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="D216" s="14">
+      <c r="D216" s="13">
         <v>12.09</v>
       </c>
       <c r="E216" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="F216" s="13">
+      <c r="F216" s="14">
         <v>6</v>
       </c>
     </row>
@@ -7073,14 +7073,14 @@
       <c r="B217" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="D217" s="14">
+      <c r="D217" s="13">
         <v>11.9</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F217" s="13">
-        <v>1</v>
+      <c r="F217" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -7088,13 +7088,13 @@
       <c r="B218" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="D218" s="14">
+      <c r="D218" s="13">
         <v>7.37</v>
       </c>
       <c r="E218" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="F218" s="13">
+      <c r="F218" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7103,14 +7103,14 @@
       <c r="B219" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="D219" s="14">
+      <c r="D219" s="13">
         <v>12.09</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="F219" s="13">
-        <v>2</v>
+      <c r="F219" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -7118,13 +7118,13 @@
       <c r="B220" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="D220" s="14">
+      <c r="D220" s="13">
         <v>12.34</v>
       </c>
       <c r="E220" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="F220" s="13">
+      <c r="F220" s="14">
         <v>2</v>
       </c>
     </row>
@@ -7133,13 +7133,13 @@
       <c r="B221" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="D221" s="14">
+      <c r="D221" s="13">
         <v>12.34</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F221" s="13">
+      <c r="F221" s="14">
         <v>3</v>
       </c>
     </row>
@@ -7148,13 +7148,13 @@
       <c r="B222" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="D222" s="14">
+      <c r="D222" s="13">
         <v>12.780000000000001</v>
       </c>
       <c r="E222" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="F222" s="13">
+      <c r="F222" s="14">
         <v>3</v>
       </c>
     </row>
@@ -7163,13 +7163,13 @@
       <c r="B223" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="D223" s="14">
+      <c r="D223" s="13">
         <v>13.620000000000001</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="F223" s="13">
+      <c r="F223" s="14">
         <v>4</v>
       </c>
     </row>
@@ -7178,13 +7178,13 @@
       <c r="B224" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="D224" s="14">
+      <c r="D224" s="13">
         <v>2.4700000000000002</v>
       </c>
       <c r="E224" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="F224" s="13">
+      <c r="F224" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7193,13 +7193,13 @@
       <c r="B225" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="D225" s="14">
+      <c r="D225" s="13">
         <v>15.35</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="F225" s="13">
+      <c r="F225" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7208,13 +7208,13 @@
       <c r="B226" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="D226" s="14">
+      <c r="D226" s="13">
         <v>12.09</v>
       </c>
       <c r="E226" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="F226" s="13">
+      <c r="F226" s="14">
         <v>6</v>
       </c>
     </row>
@@ -7223,13 +7223,13 @@
       <c r="B227" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="D227" s="14">
+      <c r="D227" s="13">
         <v>7.48</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="F227" s="13">
+      <c r="F227" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7238,13 +7238,13 @@
       <c r="B228" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="D228" s="14">
+      <c r="D228" s="13">
         <v>10.9</v>
       </c>
       <c r="E228" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="F228" s="13">
+      <c r="F228" s="14">
         <v>1</v>
       </c>
     </row>
@@ -7253,13 +7253,13 @@
       <c r="B229" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="D229" s="14">
+      <c r="D229" s="13">
         <v>15.21</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="F229" s="13">
+      <c r="F229" s="14">
         <v>2</v>
       </c>
     </row>
@@ -7268,13 +7268,13 @@
       <c r="B230" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="D230" s="14">
+      <c r="D230" s="13">
         <v>3.0300000000000002</v>
       </c>
       <c r="E230" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="F230" s="13">
+      <c r="F230" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7283,13 +7283,13 @@
       <c r="B231" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="D231" s="14">
+      <c r="D231" s="13">
         <v>5.18</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="F231" s="13">
+      <c r="F231" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7298,13 +7298,13 @@
       <c r="B232" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="D232" s="14">
+      <c r="D232" s="13">
         <v>9.5500000000000007</v>
       </c>
       <c r="E232" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="F232" s="13">
+      <c r="F232" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7313,13 +7313,13 @@
       <c r="B233" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="D233" s="14">
+      <c r="D233" s="13">
         <v>9.5500000000000007</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="F233" s="13">
+      <c r="F233" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7328,13 +7328,13 @@
       <c r="B234" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="D234" s="14">
+      <c r="D234" s="13">
         <v>5.15</v>
       </c>
       <c r="E234" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F234" s="13">
+      <c r="F234" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7343,13 +7343,13 @@
       <c r="B235" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="D235" s="14">
+      <c r="D235" s="13">
         <v>5.67</v>
       </c>
       <c r="E235" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="F235" s="13">
+      <c r="F235" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7358,13 +7358,13 @@
       <c r="B236" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="D236" s="14">
+      <c r="D236" s="13">
         <v>5.15</v>
       </c>
       <c r="E236" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F236" s="13">
+      <c r="F236" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7373,13 +7373,13 @@
       <c r="B237" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="D237" s="14">
+      <c r="D237" s="13">
         <v>18</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="F237" s="13">
+      <c r="F237" s="14">
         <v>4</v>
       </c>
     </row>
@@ -7388,13 +7388,13 @@
       <c r="B238" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="D238" s="14">
+      <c r="D238" s="13">
         <v>4.99</v>
       </c>
       <c r="E238" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="F238" s="13">
+      <c r="F238" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7403,13 +7403,13 @@
       <c r="B239" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="D239" s="14">
+      <c r="D239" s="13">
         <v>6.24</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F239" s="13">
+      <c r="F239" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7418,13 +7418,13 @@
       <c r="B240" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="D240" s="14">
+      <c r="D240" s="13">
         <v>8.39</v>
       </c>
       <c r="E240" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="F240" s="13">
+      <c r="F240" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7433,13 +7433,13 @@
       <c r="B241" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="D241" s="14">
+      <c r="D241" s="13">
         <v>7.95</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="F241" s="13">
+      <c r="F241" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7448,13 +7448,13 @@
       <c r="B242" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="D242" s="14">
+      <c r="D242" s="13">
         <v>13.3</v>
       </c>
       <c r="E242" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="F242" s="13">
+      <c r="F242" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7463,13 +7463,13 @@
       <c r="B243" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="D243" s="14">
+      <c r="D243" s="13">
         <v>4.4800000000000004</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="F243" s="13">
+      <c r="F243" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7478,13 +7478,13 @@
       <c r="B244" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="D244" s="14">
+      <c r="D244" s="13">
         <v>9.2799999999999994</v>
       </c>
       <c r="E244" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F244" s="13">
+      <c r="F244" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7493,13 +7493,13 @@
       <c r="B245" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="D245" s="14">
+      <c r="D245" s="13">
         <v>9.2799999999999994</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="F245" s="13">
+      <c r="F245" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7508,13 +7508,13 @@
       <c r="B246" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="D246" s="14">
+      <c r="D246" s="13">
         <v>4.7300000000000004</v>
       </c>
       <c r="E246" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="F246" s="13">
+      <c r="F246" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7523,13 +7523,13 @@
       <c r="B247" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="D247" s="14">
+      <c r="D247" s="13">
         <v>4.99</v>
       </c>
       <c r="E247" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="F247" s="13">
+      <c r="F247" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7538,13 +7538,13 @@
       <c r="B248" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="D248" s="14">
+      <c r="D248" s="13">
         <v>7.5600000000000005</v>
       </c>
       <c r="E248" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F248" s="13">
+      <c r="F248" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7553,13 +7553,13 @@
       <c r="B249" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D249" s="14">
+      <c r="D249" s="13">
         <v>14.31</v>
       </c>
       <c r="E249" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F249" s="13">
+      <c r="F249" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7568,13 +7568,13 @@
       <c r="B250" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="D250" s="14">
+      <c r="D250" s="13">
         <v>15.35</v>
       </c>
       <c r="E250" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="F250" s="13">
+      <c r="F250" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7583,13 +7583,13 @@
       <c r="B251" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="D251" s="14">
+      <c r="D251" s="13">
         <v>20.56</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="F251" s="13">
+      <c r="F251" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7598,13 +7598,13 @@
       <c r="B252" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="D252" s="14">
+      <c r="D252" s="13">
         <v>20.56</v>
       </c>
       <c r="E252" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="F252" s="13">
+      <c r="F252" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7613,13 +7613,13 @@
       <c r="B253" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="D253" s="14">
+      <c r="D253" s="13">
         <v>20.56</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="F253" s="13">
+      <c r="F253" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7628,13 +7628,13 @@
       <c r="B254" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="D254" s="14">
+      <c r="D254" s="13">
         <v>15.35</v>
       </c>
       <c r="E254" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="F254" s="13">
+      <c r="F254" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7643,13 +7643,13 @@
       <c r="B255" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="D255" s="14">
+      <c r="D255" s="13">
         <v>15.35</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="F255" s="13">
+      <c r="F255" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7658,13 +7658,13 @@
       <c r="B256" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="D256" s="14">
+      <c r="D256" s="13">
         <v>4.49</v>
       </c>
       <c r="E256" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="F256" s="13">
+      <c r="F256" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7673,13 +7673,13 @@
       <c r="B257" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="D257" s="14">
+      <c r="D257" s="13">
         <v>7.67</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="F257" s="13">
+      <c r="F257" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7688,13 +7688,13 @@
       <c r="B258" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="D258" s="14">
+      <c r="D258" s="13">
         <v>7.72</v>
       </c>
       <c r="E258" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="F258" s="13">
+      <c r="F258" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7703,13 +7703,13 @@
       <c r="B259" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="D259" s="14">
+      <c r="D259" s="13">
         <v>6.38</v>
       </c>
       <c r="E259" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="F259" s="13">
+      <c r="F259" s="14">
         <v>1</v>
       </c>
     </row>
@@ -7718,13 +7718,13 @@
       <c r="B260" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="D260" s="14">
+      <c r="D260" s="13">
         <v>12.620000000000001</v>
       </c>
       <c r="E260" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="F260" s="13">
+      <c r="F260" s="14">
         <v>1</v>
       </c>
     </row>
@@ -7733,13 +7733,13 @@
       <c r="B261" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="D261" s="14">
+      <c r="D261" s="13">
         <v>21.85</v>
       </c>
       <c r="E261" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="F261" s="13">
+      <c r="F261" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7748,13 +7748,13 @@
       <c r="B262" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="D262" s="14">
+      <c r="D262" s="13">
         <v>3.24</v>
       </c>
       <c r="E262" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="F262" s="13">
+      <c r="F262" s="14">
         <v>3</v>
       </c>
     </row>
@@ -7763,13 +7763,13 @@
       <c r="B263" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="D263" s="14">
+      <c r="D263" s="13">
         <v>12</v>
       </c>
       <c r="E263" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="F263" s="13">
+      <c r="F263" s="14">
         <v>2</v>
       </c>
     </row>
@@ -7778,13 +7778,13 @@
       <c r="B264" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="D264" s="14">
+      <c r="D264" s="13">
         <v>10.32</v>
       </c>
       <c r="E264" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F264" s="13">
+      <c r="F264" s="14">
         <v>2</v>
       </c>
     </row>
@@ -7793,13 +7793,13 @@
       <c r="B265" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="D265" s="14">
+      <c r="D265" s="13">
         <v>22.95</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="F265" s="13">
+      <c r="F265" s="14">
         <v>5</v>
       </c>
     </row>
@@ -7808,13 +7808,13 @@
       <c r="B266" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="D266" s="14">
+      <c r="D266" s="13">
         <v>25.55</v>
       </c>
       <c r="E266" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="F266" s="13">
+      <c r="F266" s="14">
         <v>1</v>
       </c>
     </row>
@@ -7823,13 +7823,13 @@
       <c r="B267" s="10" t="s">
         <v>551</v>
       </c>
-      <c r="D267" s="14">
+      <c r="D267" s="13">
         <v>8.3000000000000007</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="F267" s="13">
+      <c r="F267" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7838,13 +7838,13 @@
       <c r="B268" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="D268" s="14">
+      <c r="D268" s="13">
         <v>10.88</v>
       </c>
       <c r="E268" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="F268" s="13">
+      <c r="F268" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7853,13 +7853,13 @@
       <c r="B269" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="D269" s="14">
+      <c r="D269" s="13">
         <v>5.75</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="F269" s="13">
+      <c r="F269" s="14">
         <v>12</v>
       </c>
     </row>
@@ -7868,13 +7868,13 @@
       <c r="B270" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="D270" s="14">
+      <c r="D270" s="13">
         <v>4.2700000000000005</v>
       </c>
       <c r="E270" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="F270" s="13">
+      <c r="F270" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7883,13 +7883,13 @@
       <c r="B271" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="D271" s="14">
+      <c r="D271" s="13">
         <v>8.4700000000000006</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F271" s="13">
+      <c r="F271" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7898,13 +7898,13 @@
       <c r="B272" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="D272" s="14">
+      <c r="D272" s="13">
         <v>5.36</v>
       </c>
       <c r="E272" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="F272" s="13">
+      <c r="F272" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7913,13 +7913,13 @@
       <c r="B273" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="D273" s="14">
+      <c r="D273" s="13">
         <v>10.3</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F273" s="13">
+      <c r="F273" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7928,13 +7928,13 @@
       <c r="B274" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="D274" s="14">
+      <c r="D274" s="13">
         <v>5.6000000000000005</v>
       </c>
       <c r="E274" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="F274" s="13">
+      <c r="F274" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7943,13 +7943,13 @@
       <c r="B275" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="D275" s="14">
+      <c r="D275" s="13">
         <v>12.39</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="F275" s="13">
+      <c r="F275" s="14">
         <v>5</v>
       </c>
     </row>
@@ -7958,13 +7958,13 @@
       <c r="B276" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="D276" s="14">
+      <c r="D276" s="13">
         <v>12.39</v>
       </c>
       <c r="E276" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="F276" s="13">
+      <c r="F276" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7973,13 +7973,13 @@
       <c r="B277" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="D277" s="14">
+      <c r="D277" s="13">
         <v>12.39</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="F277" s="13">
+      <c r="F277" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7988,13 +7988,13 @@
       <c r="B278" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="D278" s="14">
+      <c r="D278" s="13">
         <v>12.39</v>
       </c>
       <c r="E278" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="F278" s="13">
+      <c r="F278" s="14">
         <v>0</v>
       </c>
     </row>
@@ -8008,13 +8008,13 @@
       <c r="C279" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="D279" s="14">
+      <c r="D279" s="13">
         <v>18.38</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F279" s="13">
+      <c r="F279" s="14">
         <v>3</v>
       </c>
     </row>
@@ -8028,13 +8028,13 @@
       <c r="C280" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="D280" s="14">
+      <c r="D280" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E280" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F280" s="13">
+      <c r="F280" s="14">
         <v>2</v>
       </c>
     </row>
@@ -8048,13 +8048,13 @@
       <c r="C281" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="D281" s="14">
+      <c r="D281" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="F281" s="13">
+      <c r="F281" s="14">
         <v>5</v>
       </c>
     </row>
@@ -8068,13 +8068,13 @@
       <c r="C282" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="D282" s="14">
+      <c r="D282" s="13">
         <v>18.38</v>
       </c>
       <c r="E282" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="F282" s="13">
+      <c r="F282" s="14">
         <v>3</v>
       </c>
     </row>
@@ -8088,14 +8088,14 @@
       <c r="C283" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="D283" s="14">
+      <c r="D283" s="13">
         <v>16.899999999999999</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="F283" s="13">
-        <v>2</v>
+      <c r="F283" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/motip-spray.xlsx
+++ b/prix/motip-spray.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79CFC80-D447-47BE-BFC2-E874BB024B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0668ED9-7646-4DE1-AAC5-4F2A25FE9F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -3135,7 +3135,7 @@
         <v>20</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -3475,7 +3475,7 @@
         <v>37</v>
       </c>
       <c r="F33" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3675,7 +3675,7 @@
         <v>47</v>
       </c>
       <c r="F43" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3995,7 +3995,7 @@
         <v>63</v>
       </c>
       <c r="F59" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -4175,7 +4175,7 @@
         <v>72</v>
       </c>
       <c r="F68" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -4275,7 +4275,7 @@
         <v>77</v>
       </c>
       <c r="F73" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -5095,7 +5095,7 @@
         <v>118</v>
       </c>
       <c r="F114" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -5155,7 +5155,7 @@
         <v>121</v>
       </c>
       <c r="F117" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -5555,7 +5555,7 @@
         <v>141</v>
       </c>
       <c r="F137" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -5715,7 +5715,7 @@
         <v>149</v>
       </c>
       <c r="F145" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -6475,7 +6475,7 @@
         <v>187</v>
       </c>
       <c r="F183" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -6635,7 +6635,7 @@
         <v>195</v>
       </c>
       <c r="F191" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -6775,7 +6775,7 @@
         <v>202</v>
       </c>
       <c r="F198" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -6870,7 +6870,7 @@
         <v>207</v>
       </c>
       <c r="F203" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
@@ -7065,7 +7065,7 @@
         <v>220</v>
       </c>
       <c r="F216" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -7110,7 +7110,7 @@
         <v>223</v>
       </c>
       <c r="F219" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -7245,7 +7245,7 @@
         <v>232</v>
       </c>
       <c r="F228" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -7260,7 +7260,7 @@
         <v>233</v>
       </c>
       <c r="F229" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/motip-spray.xlsx
+++ b/prix/motip-spray.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0668ED9-7646-4DE1-AAC5-4F2A25FE9F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A784311-46D7-4D81-9B05-D9E0664AF918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -2857,7 +2857,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -3215,7 +3215,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -3475,7 +3475,7 @@
         <v>37</v>
       </c>
       <c r="F33" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3515,7 +3515,7 @@
         <v>39</v>
       </c>
       <c r="F35" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -3675,7 +3675,7 @@
         <v>47</v>
       </c>
       <c r="F43" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3715,7 +3715,7 @@
         <v>49</v>
       </c>
       <c r="F45" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -4095,7 +4095,7 @@
         <v>68</v>
       </c>
       <c r="F64" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -4175,7 +4175,7 @@
         <v>72</v>
       </c>
       <c r="F68" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -4269,13 +4269,13 @@
         <v>689</v>
       </c>
       <c r="D73" s="13">
-        <v>9.66</v>
+        <v>14.65</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>77</v>
       </c>
       <c r="F73" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -5055,7 +5055,7 @@
         <v>116</v>
       </c>
       <c r="F112" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -6415,7 +6415,7 @@
         <v>184</v>
       </c>
       <c r="F180" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -6755,7 +6755,7 @@
         <v>201</v>
       </c>
       <c r="F197" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -6775,7 +6775,7 @@
         <v>202</v>
       </c>
       <c r="F198" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -6815,7 +6815,7 @@
         <v>204</v>
       </c>
       <c r="F200" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
@@ -6975,7 +6975,7 @@
         <v>214</v>
       </c>
       <c r="F210" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -7065,7 +7065,7 @@
         <v>220</v>
       </c>
       <c r="F216" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -7110,7 +7110,7 @@
         <v>223</v>
       </c>
       <c r="F219" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
